--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/auth-controller/logout-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/auth-controller/logout-it-form.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
-  <si>
-    <t>Statement: logout(): Promise&lt;ActionResult&lt;void&gt;&gt; — destroys the current session and returns a success result.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="47">
+  <si>
+    <t>Statement: logout(): Promise&lt;ActionResult&lt;void&gt;&gt; - destroys the current session and returns a success result.</t>
   </si>
   <si>
     <t/>
@@ -34,13 +34,13 @@
     <t>Precondition</t>
   </si>
   <si>
-    <t>A session exists and can be retrieved via getSession(). getSession() is mocked — it calls cookies() from next/headers which is a Next.js request-context primitive unavailable in Jest; the mock returns a controlled session object in its place.</t>
+    <t>A session exists and can be retrieved via getSession().</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>ActionResult&lt;void&gt; — { success: true, data: undefined } on success. { success: false, message } if session destruction throws.</t>
+    <t>ActionResult&lt;void&gt; - { success: true, data: undefined } on success. { success: false, message } if session destruction throws.</t>
   </si>
   <si>
     <t>Postcondition</t>
@@ -58,6 +58,12 @@
     <t>Tear down:  npm run test:integration:down</t>
   </si>
   <si>
+    <t>All service and repository singletons are instantiated and accessed via the lib/di module, which configures them to use the shared PrismaClient instance.</t>
+  </si>
+  <si>
+    <t>getSession() is mocked as it calls cookies() from next/headers which is a Next.js request-context primitive unavailable in Jest; the mock returns a controlled session object in its place.</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -139,7 +145,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>CTRL-2</t>
+    <t>CTRL-02</t>
   </si>
   <si>
     <t>n/a</t>
@@ -268,7 +274,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="11339512" cy="2462212"/>
+    <xdr:ext cx="11825287" cy="2462212"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -625,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -660,7 +666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="65" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -726,6 +732,22 @@
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +767,7 @@
   <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="21" width="11" customWidth="1"/>
+    <col min="1" max="22" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -793,22 +815,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -816,22 +838,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -839,22 +861,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -882,17 +904,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -904,40 +926,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -945,7 +967,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
@@ -957,28 +979,28 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
